--- a/db/data/office_cats.xlsx
+++ b/db/data/office_cats.xlsx
@@ -1,21 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
-  <workbookPr defaultThemeVersion="166925"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Pradeep\Desktop\storemgmt\db\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dell\Desktop\storemgmt\db\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50D789EF-5A9A-4874-99DF-BDD3AAB2B1A4}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-2970" yWindow="5010" windowWidth="15375" windowHeight="7875" xr2:uid="{E111373D-40DB-492C-88BA-0DB93801AA1A}"/>
+    <workbookView xWindow="-2970" yWindow="5010" windowWidth="15375" windowHeight="7875"/>
   </bookViews>
   <sheets>
     <sheet name="office_item_category" sheetId="2" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="152511"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -31,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="147">
   <si>
     <t>id</t>
   </si>
@@ -105,9 +104,6 @@
     <t>Wrenchs</t>
   </si>
   <si>
-    <t>Beds</t>
-  </si>
-  <si>
     <t>Files</t>
   </si>
   <si>
@@ -204,12 +200,6 @@
     <t>Diaries</t>
   </si>
   <si>
-    <t>Glue Sticks</t>
-  </si>
-  <si>
-    <t>Markers</t>
-  </si>
-  <si>
     <t>Staples</t>
   </si>
   <si>
@@ -222,9 +212,6 @@
     <t>Papers</t>
   </si>
   <si>
-    <t>Bulb and Switches</t>
-  </si>
-  <si>
     <t>Wires</t>
   </si>
   <si>
@@ -294,9 +281,6 @@
     <t>रेन्चहरु</t>
   </si>
   <si>
-    <t>खाट</t>
-  </si>
-  <si>
     <t>फायल</t>
   </si>
   <si>
@@ -411,12 +395,6 @@
     <t>फाईल</t>
   </si>
   <si>
-    <t>ग्लु स्टिक</t>
-  </si>
-  <si>
-    <t>मार्कर</t>
-  </si>
-  <si>
     <t>स्टेपल</t>
   </si>
   <si>
@@ -429,9 +407,6 @@
     <t>कागज</t>
   </si>
   <si>
-    <t>बल्ब, स्विच</t>
-  </si>
-  <si>
     <t>किताव</t>
   </si>
   <si>
@@ -466,12 +441,42 @@
   </si>
   <si>
     <t>Jack/Welding Machines</t>
+  </si>
+  <si>
+    <t>Reports</t>
+  </si>
+  <si>
+    <t>प्रतिवेदनहरू</t>
+  </si>
+  <si>
+    <t>Electric Accessories</t>
+  </si>
+  <si>
+    <t>Tyre</t>
+  </si>
+  <si>
+    <t>टायर</t>
+  </si>
+  <si>
+    <t>Beds and Related</t>
+  </si>
+  <si>
+    <t>विस्तारा र सम्बन्धित</t>
+  </si>
+  <si>
+    <t>विद्युतीय सामाग्रीहरु</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Glue Sticks &amp; Tape </t>
+  </si>
+  <si>
+    <t>ग्लु स्टिक एण्ड टेप</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -816,8 +821,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B9CD248-BFF2-433C-A70D-90987FB8172E}">
-  <dimension ref="A1:F68"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:F69"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="30.5703125" bestFit="1" customWidth="1"/>
@@ -852,13 +857,13 @@
         <v>6</v>
       </c>
       <c r="D2" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="E2" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="F2" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -866,16 +871,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="s">
+        <v>61</v>
+      </c>
+      <c r="D3" t="s">
         <v>65</v>
       </c>
-      <c r="D3" t="s">
-        <v>69</v>
-      </c>
       <c r="E3" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="F3" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -886,13 +891,13 @@
         <v>7</v>
       </c>
       <c r="D4" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="E4" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="F4" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -903,13 +908,13 @@
         <v>8</v>
       </c>
       <c r="D5" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="E5" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="F5" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -920,13 +925,13 @@
         <v>9</v>
       </c>
       <c r="D6" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="E6" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="F6" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -937,13 +942,13 @@
         <v>10</v>
       </c>
       <c r="D7" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="E7" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="F7" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -954,13 +959,13 @@
         <v>11</v>
       </c>
       <c r="D8" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="E8" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="F8" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -971,13 +976,13 @@
         <v>12</v>
       </c>
       <c r="D9" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="E9" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="F9" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -988,13 +993,13 @@
         <v>13</v>
       </c>
       <c r="D10" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="E10" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="F10" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -1005,13 +1010,13 @@
         <v>14</v>
       </c>
       <c r="D11" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="E11" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="F11" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -1022,13 +1027,13 @@
         <v>15</v>
       </c>
       <c r="D12" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="E12" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="F12" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -1039,13 +1044,13 @@
         <v>16</v>
       </c>
       <c r="D13" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="E13" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="F13" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -1056,13 +1061,13 @@
         <v>17</v>
       </c>
       <c r="D14" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="E14" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="F14" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -1073,13 +1078,13 @@
         <v>18</v>
       </c>
       <c r="D15" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="E15" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="F15" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -1090,13 +1095,13 @@
         <v>19</v>
       </c>
       <c r="D16" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="E16" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="F16" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
     </row>
     <row r="17" spans="2:6" x14ac:dyDescent="0.25">
@@ -1107,13 +1112,13 @@
         <v>20</v>
       </c>
       <c r="D17" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="E17" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="F17" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
     </row>
     <row r="18" spans="2:6" x14ac:dyDescent="0.25">
@@ -1124,13 +1129,13 @@
         <v>21</v>
       </c>
       <c r="D18" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="E18" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="F18" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
     </row>
     <row r="19" spans="2:6" x14ac:dyDescent="0.25">
@@ -1141,13 +1146,13 @@
         <v>22</v>
       </c>
       <c r="D19" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="E19" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="F19" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
     </row>
     <row r="20" spans="2:6" x14ac:dyDescent="0.25">
@@ -1158,13 +1163,13 @@
         <v>23</v>
       </c>
       <c r="D20" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="E20" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="F20" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.25">
@@ -1172,16 +1177,16 @@
         <v>20</v>
       </c>
       <c r="C21" t="s">
-        <v>24</v>
+        <v>142</v>
       </c>
       <c r="D21" t="s">
-        <v>87</v>
+        <v>143</v>
       </c>
       <c r="E21" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="F21" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.25">
@@ -1189,16 +1194,16 @@
         <v>21</v>
       </c>
       <c r="C22" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D22" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="E22" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="F22" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
     </row>
     <row r="23" spans="2:6" x14ac:dyDescent="0.25">
@@ -1206,16 +1211,16 @@
         <v>22</v>
       </c>
       <c r="C23" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D23" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="E23" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="F23" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
     </row>
     <row r="24" spans="2:6" x14ac:dyDescent="0.25">
@@ -1223,16 +1228,16 @@
         <v>23</v>
       </c>
       <c r="C24" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D24" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="E24" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="F24" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
     </row>
     <row r="25" spans="2:6" x14ac:dyDescent="0.25">
@@ -1240,16 +1245,16 @@
         <v>24</v>
       </c>
       <c r="C25" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D25" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="E25" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="F25" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
     </row>
     <row r="26" spans="2:6" x14ac:dyDescent="0.25">
@@ -1257,16 +1262,16 @@
         <v>25</v>
       </c>
       <c r="C26" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D26" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="E26" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="F26" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
     </row>
     <row r="27" spans="2:6" x14ac:dyDescent="0.25">
@@ -1274,16 +1279,16 @@
         <v>26</v>
       </c>
       <c r="C27" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D27" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="E27" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="F27" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
     </row>
     <row r="28" spans="2:6" x14ac:dyDescent="0.25">
@@ -1291,16 +1296,16 @@
         <v>27</v>
       </c>
       <c r="C28" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D28" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="E28" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="F28" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.25">
@@ -1308,16 +1313,16 @@
         <v>28</v>
       </c>
       <c r="C29" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D29" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="E29" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="F29" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.25">
@@ -1325,16 +1330,16 @@
         <v>29</v>
       </c>
       <c r="C30" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D30" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="E30" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="F30" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
     </row>
     <row r="31" spans="2:6" x14ac:dyDescent="0.25">
@@ -1342,16 +1347,16 @@
         <v>30</v>
       </c>
       <c r="C31" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D31" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="E31" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="F31" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
     </row>
     <row r="32" spans="2:6" x14ac:dyDescent="0.25">
@@ -1359,16 +1364,16 @@
         <v>31</v>
       </c>
       <c r="C32" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D32" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="E32" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="F32" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.25">
@@ -1376,16 +1381,16 @@
         <v>32</v>
       </c>
       <c r="C33" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D33" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="E33" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="F33" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
     </row>
     <row r="34" spans="2:6" x14ac:dyDescent="0.25">
@@ -1393,16 +1398,16 @@
         <v>33</v>
       </c>
       <c r="C34" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D34" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="E34" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="F34" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
     </row>
     <row r="35" spans="2:6" x14ac:dyDescent="0.25">
@@ -1410,16 +1415,16 @@
         <v>34</v>
       </c>
       <c r="C35" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D35" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="E35" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="F35" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
     </row>
     <row r="36" spans="2:6" x14ac:dyDescent="0.25">
@@ -1427,16 +1432,16 @@
         <v>35</v>
       </c>
       <c r="C36" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D36" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="E36" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="F36" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.25">
@@ -1444,16 +1449,16 @@
         <v>36</v>
       </c>
       <c r="C37" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D37" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="E37" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="F37" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.25">
@@ -1461,16 +1466,16 @@
         <v>37</v>
       </c>
       <c r="C38" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D38" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="E38" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="F38" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.25">
@@ -1478,16 +1483,16 @@
         <v>38</v>
       </c>
       <c r="C39" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D39" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="E39" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="F39" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.25">
@@ -1495,16 +1500,16 @@
         <v>39</v>
       </c>
       <c r="C40" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="D40" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="E40" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="F40" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
     </row>
     <row r="41" spans="2:6" x14ac:dyDescent="0.25">
@@ -1512,16 +1517,16 @@
         <v>40</v>
       </c>
       <c r="C41" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D41" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="E41" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="F41" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.25">
@@ -1529,16 +1534,16 @@
         <v>41</v>
       </c>
       <c r="C42" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D42" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="E42" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="F42" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
     </row>
     <row r="43" spans="2:6" x14ac:dyDescent="0.25">
@@ -1546,16 +1551,16 @@
         <v>42</v>
       </c>
       <c r="C43" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D43" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="E43" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="F43" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
     </row>
     <row r="44" spans="2:6" x14ac:dyDescent="0.25">
@@ -1563,16 +1568,16 @@
         <v>43</v>
       </c>
       <c r="C44" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D44" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="E44" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="F44" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.25">
@@ -1580,16 +1585,16 @@
         <v>44</v>
       </c>
       <c r="C45" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="D45" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="E45" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="F45" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.25">
@@ -1597,16 +1602,16 @@
         <v>45</v>
       </c>
       <c r="C46" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="D46" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="E46" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="F46" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
     </row>
     <row r="47" spans="2:6" x14ac:dyDescent="0.25">
@@ -1614,16 +1619,16 @@
         <v>46</v>
       </c>
       <c r="C47" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D47" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="E47" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="F47" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
     </row>
     <row r="48" spans="2:6" x14ac:dyDescent="0.25">
@@ -1631,16 +1636,16 @@
         <v>47</v>
       </c>
       <c r="C48" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D48" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="E48" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="F48" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
     </row>
     <row r="49" spans="2:6" x14ac:dyDescent="0.25">
@@ -1648,16 +1653,16 @@
         <v>48</v>
       </c>
       <c r="C49" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D49" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="E49" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="F49" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
     </row>
     <row r="50" spans="2:6" x14ac:dyDescent="0.25">
@@ -1665,16 +1670,16 @@
         <v>49</v>
       </c>
       <c r="C50" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D50" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="E50" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="F50" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.25">
@@ -1682,16 +1687,16 @@
         <v>50</v>
       </c>
       <c r="C51" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D51" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="E51" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="F51" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.25">
@@ -1699,16 +1704,16 @@
         <v>51</v>
       </c>
       <c r="C52" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D52" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="E52" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="F52" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
     </row>
     <row r="53" spans="2:6" x14ac:dyDescent="0.25">
@@ -1716,16 +1721,16 @@
         <v>52</v>
       </c>
       <c r="C53" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D53" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="E53" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="F53" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
     </row>
     <row r="54" spans="2:6" x14ac:dyDescent="0.25">
@@ -1733,16 +1738,16 @@
         <v>53</v>
       </c>
       <c r="C54" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D54" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="E54" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="F54" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
     </row>
     <row r="55" spans="2:6" x14ac:dyDescent="0.25">
@@ -1750,16 +1755,16 @@
         <v>54</v>
       </c>
       <c r="C55" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D55" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="E55" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="F55" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
     </row>
     <row r="56" spans="2:6" x14ac:dyDescent="0.25">
@@ -1767,16 +1772,16 @@
         <v>55</v>
       </c>
       <c r="C56" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D56" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="E56" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="F56" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
     </row>
     <row r="57" spans="2:6" x14ac:dyDescent="0.25">
@@ -1784,16 +1789,16 @@
         <v>56</v>
       </c>
       <c r="C57" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D57" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="E57" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="F57" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
     </row>
     <row r="58" spans="2:6" x14ac:dyDescent="0.25">
@@ -1801,189 +1806,207 @@
         <v>57</v>
       </c>
       <c r="C58" t="s">
-        <v>57</v>
+        <v>145</v>
       </c>
       <c r="D58" t="s">
-        <v>126</v>
+        <v>146</v>
       </c>
       <c r="E58" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="F58" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
     </row>
     <row r="59" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B59">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C59" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D59" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="E59" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="F59" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
     </row>
     <row r="60" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B60">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C60" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D60" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="E60" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="F60" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
     </row>
     <row r="61" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B61">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C61" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D61" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="E61" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="F61" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
     </row>
     <row r="62" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B62">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C62" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D62" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="E62" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="F62" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
     </row>
     <row r="63" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B63">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C63" t="s">
-        <v>62</v>
+        <v>139</v>
       </c>
       <c r="D63" t="s">
-        <v>131</v>
+        <v>144</v>
       </c>
       <c r="E63" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="F63" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
     </row>
     <row r="64" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B64">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C64" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D64" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="E64" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="F64" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
     </row>
     <row r="65" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B65">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C65" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="D65" t="s">
+        <v>126</v>
+      </c>
+      <c r="E65" t="s">
+        <v>127</v>
+      </c>
+      <c r="F65" t="s">
         <v>133</v>
-      </c>
-      <c r="E65" t="s">
-        <v>136</v>
-      </c>
-      <c r="F65" t="s">
-        <v>142</v>
       </c>
     </row>
     <row r="66" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B66">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C66" t="s">
-        <v>67</v>
+        <v>129</v>
       </c>
       <c r="D66" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="E66" t="s">
+        <v>131</v>
+      </c>
+      <c r="F66" t="s">
         <v>135</v>
-      </c>
-      <c r="F66" t="s">
-        <v>141</v>
       </c>
     </row>
     <row r="67" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B67">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C67" t="s">
-        <v>137</v>
+        <v>60</v>
       </c>
       <c r="D67" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="E67" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="F67" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
     </row>
     <row r="68" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B68">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C68" t="s">
-        <v>64</v>
+        <v>137</v>
       </c>
       <c r="D68" t="s">
+        <v>138</v>
+      </c>
+      <c r="E68" t="s">
+        <v>128</v>
+      </c>
+      <c r="F68" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="69" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B69">
+        <v>70</v>
+      </c>
+      <c r="C69" t="s">
         <v>140</v>
       </c>
-      <c r="E68" t="s">
-        <v>139</v>
-      </c>
-      <c r="F68" t="s">
-        <v>143</v>
+      <c r="D69" t="s">
+        <v>141</v>
+      </c>
+      <c r="E69" t="s">
+        <v>128</v>
+      </c>
+      <c r="F69" t="s">
+        <v>134</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>